--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66196C22-7445-4081-B40E-FB2322DCB030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F11EAEB-E4A0-4AF8-B437-51D0E93E6104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,13 +747,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH06,S02aH03,S05aH07,S04aH05,S04aH08,S02aH02,S06aH06,S01aH03,S05aH02,S05aH03,S05aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH04,S02aH05,S06aH07,S01aH04,S01aH07,S02aH07,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH03,S05aH08,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03,S03aH04,S04aH02,S01aH02,S04aH04</t>
+    <t>S03aH04,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S03aH02,S03aH03,S01aH02,S04aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH02,S01aH03,S05aH02,S05aH03,S05aH06,S04aH06,S05aH04,S06aH02,S06aH03,S04aH05,S04aH08,S04aH03,S05aH08,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S06aH02,S05aH08,S03aH01,S01aH02,S05aH10,S03aH08,S03aH10,S06aH08,S01aH09,S04aH02,S03aH09,S05aH09,S02aH02,S04aH10,S06aH10,S04aH08,S06aH01,S02aH01,S02aH10,S05aH02,S06aH09,S02aH09,S04aH09,S05aH01,S01aH10,S03aH02,S01aH08,S02aH08</t>
+    <t>S02aH09,S04aH09,S05aH01,S03aH01,S01aH01,S04aH01,S06aH02,S04aH02,S02aH02,S04aH10,S06aH10,S01aH08,S02aH08,S01aH02,S05aH10,S01aH10,S03aH02,S06aH09,S05aH08,S02aH01,S02aH10,S05aH02,S04aH08,S06aH01,S01aH09,S03aH08,S03aH10,S06aH08,S03aH09,S05aH09</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH01,S04aH01,S06aH02,S05aH08,S03aH01,S01aH02,S05aH10,S03aH08,S03aH10,S06aH08,S01aH09,S04aH02,S03aH09,S05aH09,S02aH02,S04aH10,S06aH10,S04aH08,S06aH01,S02aH01,S02aH10,S05aH02,S06aH09,S02aH09,S04aH09,S05aH01,S01aH10,S03aH02,S01aH08,S02aH08</v>
+        <v>S02aH09,S04aH09,S05aH01,S03aH01,S01aH01,S04aH01,S06aH02,S04aH02,S02aH02,S04aH10,S06aH10,S01aH08,S02aH08,S01aH02,S05aH10,S01aH10,S03aH02,S06aH09,S05aH08,S02aH01,S02aH10,S05aH02,S04aH08,S06aH01,S01aH09,S03aH08,S03aH10,S06aH08,S03aH09,S05aH09</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH06,S02aH03,S05aH07,S04aH05,S04aH08,S02aH02,S06aH06,S01aH03,S05aH02,S05aH03,S05aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH04,S02aH05,S06aH07,S01aH04,S01aH07,S02aH07,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH03,S05aH08,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03,S03aH04,S04aH02,S01aH02,S04aH04</v>
+        <v>S03aH04,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S03aH02,S03aH03,S01aH02,S04aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH02,S01aH03,S05aH02,S05aH03,S05aH06,S04aH06,S05aH04,S06aH02,S06aH03,S04aH05,S04aH08,S04aH03,S05aH08,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1476,7 +1476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2AF6A8F-7CDF-46C6-ACED-2D5B38777391}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B77B42CC-8B18-4D83-BFD5-B168F7EF1E2C}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1620,7 +1620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629631B6-E4A0-4A92-B8CA-7AE5FE04E488}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B7C31F-4D09-46D0-8AD7-9C0A2AE0E1CA}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40082,7 +40082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F88F71-D299-4118-8DEC-3968B2DBB126}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9199800C-705F-41C6-9858-790942F45C90}">
   <dimension ref="B9:IV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61135,7 +61135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F725A1-C922-4E13-837A-B1FCF8ECD7D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB8CAA5-55BB-4625-9833-30BF00AD6E53}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62005,7 +62005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85105799-1F74-43AD-8E53-FE804D34CC8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1585D03F-BD38-4C2D-81AE-4E9A51F7BF47}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -63352,7 +63352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2DBAAA-4228-4AA0-8183-587B23396A76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6FDAD61-DD88-4424-AA6D-0C183B3BB5B1}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64039,7 +64039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B891406E-4440-4F8B-B179-17E7F2FAE3C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{084A7A8A-7337-40B1-AC08-1F199FB8FCB3}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
